--- a/figures/common/wbs_v2.xlsx
+++ b/figures/common/wbs_v2.xlsx
@@ -71,7 +71,7 @@
       <sz val="8.5"/>
     </font>
   </fonts>
-  <fills count="20">
+  <fills count="24">
     <fill>
       <patternFill/>
     </fill>
@@ -166,6 +166,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF0C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD966"/>
+        <bgColor rgb="00FFD966"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009DC3E6"/>
+        <bgColor rgb="009DC3E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E75B6"/>
+        <bgColor rgb="002E75B6"/>
       </patternFill>
     </fill>
   </fills>
@@ -414,7 +438,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -534,6 +558,15 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -899,7 +932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -907,7 +940,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -1127,25 +1160,19 @@
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="8" t="n"/>
       <c r="B12" s="8" t="n"/>
-      <c r="C12" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>担当B設計（センサー・観測）</t>
-        </is>
-      </c>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
       <c r="E12" s="5" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>赤外線センサー配線設計</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>長野・慶田</t>
+          <t>Processing GUI設計（楽器指定・BPM・START/STOP）</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>長見・飛田</t>
         </is>
       </c>
     </row>
@@ -1155,11 +1182,11 @@
       <c r="C13" s="8" t="n"/>
       <c r="D13" s="8" t="n"/>
       <c r="E13" s="5" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>フォトTr配線設計</t>
+          <t>シリアル通信コマンド設計（INSTRUMENT/BPM）</t>
         </is>
       </c>
       <c r="G13" s="8" t="n"/>
@@ -1170,11 +1197,11 @@
       <c r="C14" s="8" t="n"/>
       <c r="D14" s="8" t="n"/>
       <c r="E14" s="5" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>センサーISR設計</t>
+          <t>赤外線センサー配線設計</t>
         </is>
       </c>
       <c r="G14" s="8" t="n"/>
@@ -1185,11 +1212,11 @@
       <c r="C15" s="8" t="n"/>
       <c r="D15" s="8" t="n"/>
       <c r="E15" s="5" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>テンポ推定アルゴリズム設計</t>
+          <t>フォトTr配線設計</t>
         </is>
       </c>
       <c r="G15" s="8" t="n"/>
@@ -1200,11 +1227,11 @@
       <c r="C16" s="9" t="n"/>
       <c r="D16" s="9" t="n"/>
       <c r="E16" s="5" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>状態機械設計</t>
+          <t>センサーISR設計</t>
         </is>
       </c>
       <c r="G16" s="9" t="n"/>
@@ -1212,27 +1239,17 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="8" t="n"/>
       <c r="B17" s="8" t="n"/>
-      <c r="C17" s="3" t="n">
-        <v>140</v>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>担当C設計（演奏制御）</t>
-        </is>
-      </c>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
       <c r="E17" s="5" t="n">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>拍検出・オフセット設計</t>
-        </is>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>長山・慶田</t>
-        </is>
-      </c>
+          <t>テンポ推定アルゴリズム設計</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="8" t="n"/>
@@ -1240,11 +1257,11 @@
       <c r="C18" s="8" t="n"/>
       <c r="D18" s="8" t="n"/>
       <c r="E18" s="5" t="n">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>楽譜進行制御設計</t>
+          <t>状態機械設計</t>
         </is>
       </c>
       <c r="G18" s="8" t="n"/>
@@ -1255,11 +1272,11 @@
       <c r="C19" s="8" t="n"/>
       <c r="D19" s="8" t="n"/>
       <c r="E19" s="5" t="n">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>シリアル送信プロトコル設計</t>
+          <t>キャリブレーション手順設計（CALIBRATE状態）</t>
         </is>
       </c>
       <c r="G19" s="8" t="n"/>
@@ -1270,11 +1287,11 @@
       <c r="C20" s="9" t="n"/>
       <c r="D20" s="9" t="n"/>
       <c r="E20" s="5" t="n">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>楽譜配列定義・5パート</t>
+          <t>INSTRUMENT_ID輝度キュー設計</t>
         </is>
       </c>
       <c r="G20" s="9" t="n"/>
@@ -1283,24 +1300,24 @@
       <c r="A21" s="8" t="n"/>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="3" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>担当D設計（音響合成）</t>
+          <t>担当C設計（演奏制御）</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>シリアル受信処理設計</t>
-        </is>
-      </c>
-      <c r="G21" s="13" t="inlineStr">
-        <is>
-          <t>中村・尾添</t>
+          <t>拍検出・オフセット設計</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>長山・慶田</t>
         </is>
       </c>
     </row>
@@ -1310,11 +1327,11 @@
       <c r="C22" s="8" t="n"/>
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="5" t="n">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>音色合成エンジン設計</t>
+          <t>楽譜進行制御設計</t>
         </is>
       </c>
       <c r="G22" s="8" t="n"/>
@@ -1325,11 +1342,11 @@
       <c r="C23" s="8" t="n"/>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="5" t="n">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>エフェクト・フェルマータ延奏設計</t>
+          <t>シリアル送信プロトコル設計</t>
         </is>
       </c>
       <c r="G23" s="8" t="n"/>
@@ -1340,11 +1357,11 @@
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="5" t="n">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>音色定義シート作成</t>
+          <t>楽譜配列定義・5パート</t>
         </is>
       </c>
       <c r="G24" s="8" t="n"/>
@@ -1355,45 +1372,29 @@
       <c r="C25" s="9" t="n"/>
       <c r="D25" s="9" t="n"/>
       <c r="E25" s="5" t="n">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>ADSRパラメータ仕様策定</t>
+          <t>シリアル受信処理設計</t>
         </is>
       </c>
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>実装フェーズ</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>210</v>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>担当A実装（指揮者人形ユニット）</t>
-        </is>
-      </c>
+      <c r="A26" s="8" t="n"/>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
       <c r="E26" s="5" t="n">
-        <v>211</v>
+        <v>152</v>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>サーボ機構組み立て</t>
-        </is>
-      </c>
-      <c r="G26" s="10" t="inlineStr">
-        <is>
-          <t>長見・飛田</t>
-        </is>
-      </c>
+          <t>音色合成エンジン設計</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="8" t="n"/>
@@ -1401,11 +1402,11 @@
       <c r="C27" s="8" t="n"/>
       <c r="D27" s="8" t="n"/>
       <c r="E27" s="5" t="n">
-        <v>212</v>
+        <v>153</v>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>腕・反射板取り付け</t>
+          <t>エフェクト・フェルマータ延奏設計</t>
         </is>
       </c>
       <c r="G27" s="8" t="n"/>
@@ -1416,11 +1417,11 @@
       <c r="C28" s="8" t="n"/>
       <c r="D28" s="8" t="n"/>
       <c r="E28" s="5" t="n">
-        <v>213</v>
+        <v>154</v>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>LED駆動回路配線</t>
+          <t>音色定義シート作成</t>
         </is>
       </c>
       <c r="G28" s="8" t="n"/>
@@ -1431,11 +1432,11 @@
       <c r="C29" s="8" t="n"/>
       <c r="D29" s="8" t="n"/>
       <c r="E29" s="5" t="n">
-        <v>214</v>
+        <v>155</v>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>サーボ駆動回路配線</t>
+          <t>ADSRパラメータ仕様策定</t>
         </is>
       </c>
       <c r="G29" s="8" t="n"/>
@@ -1446,11 +1447,11 @@
       <c r="C30" s="8" t="n"/>
       <c r="D30" s="8" t="n"/>
       <c r="E30" s="5" t="n">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>サーボ制御SW実装</t>
+          <t>サーボ機構組み立て</t>
         </is>
       </c>
       <c r="G30" s="8" t="n"/>
@@ -1458,42 +1459,32 @@
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="8" t="n"/>
       <c r="B31" s="8" t="n"/>
-      <c r="C31" s="9" t="n"/>
-      <c r="D31" s="9" t="n"/>
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="8" t="n"/>
       <c r="E31" s="5" t="n">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>輝度エンコードLED制御SW実装</t>
-        </is>
-      </c>
-      <c r="G31" s="9" t="n"/>
+          <t>腕・反射板取り付け</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="8" t="n"/>
       <c r="B32" s="8" t="n"/>
-      <c r="C32" s="3" t="n">
-        <v>220</v>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>担当B実装（センサー・観測）</t>
-        </is>
-      </c>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="9" t="n"/>
       <c r="E32" s="5" t="n">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>赤外線センサー配線</t>
-        </is>
-      </c>
-      <c r="G32" s="11" t="inlineStr">
-        <is>
-          <t>長野・慶田</t>
-        </is>
-      </c>
+          <t>LED駆動回路配線</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="8" t="n"/>
@@ -1501,11 +1492,11 @@
       <c r="C33" s="8" t="n"/>
       <c r="D33" s="8" t="n"/>
       <c r="E33" s="5" t="n">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>フォトTr配線・遮光チャンバー</t>
+          <t>サーボ駆動回路配線</t>
         </is>
       </c>
       <c r="G33" s="8" t="n"/>
@@ -1516,11 +1507,11 @@
       <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="n"/>
       <c r="E34" s="5" t="n">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>センサーISR実装</t>
+          <t>サーボ制御SW実装</t>
         </is>
       </c>
       <c r="G34" s="8" t="n"/>
@@ -1531,11 +1522,11 @@
       <c r="C35" s="8" t="n"/>
       <c r="D35" s="8" t="n"/>
       <c r="E35" s="5" t="n">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>テンポ推定実装</t>
+          <t>輝度エンコードLED制御SW実装</t>
         </is>
       </c>
       <c r="G35" s="8" t="n"/>
@@ -1546,11 +1537,11 @@
       <c r="C36" s="9" t="n"/>
       <c r="D36" s="9" t="n"/>
       <c r="E36" s="5" t="n">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>状態機械実装</t>
+          <t>Processing GUI実装</t>
         </is>
       </c>
       <c r="G36" s="9" t="n"/>
@@ -1558,25 +1549,19 @@
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="8" t="n"/>
       <c r="B37" s="8" t="n"/>
-      <c r="C37" s="3" t="n">
-        <v>230</v>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>担当C実装（演奏制御）</t>
-        </is>
-      </c>
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="9" t="n"/>
       <c r="E37" s="5" t="n">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>拍検出・オフセット実装</t>
-        </is>
-      </c>
-      <c r="G37" s="12" t="inlineStr">
-        <is>
-          <t>長山・慶田</t>
+          <t>シリアル通信実装（PC→Arduino）</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>長見・飛田</t>
         </is>
       </c>
     </row>
@@ -1586,11 +1571,11 @@
       <c r="C38" s="8" t="n"/>
       <c r="D38" s="8" t="n"/>
       <c r="E38" s="5" t="n">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>楽譜進行制御実装</t>
+          <t>赤外線センサー配線</t>
         </is>
       </c>
       <c r="G38" s="8" t="n"/>
@@ -1601,11 +1586,11 @@
       <c r="C39" s="8" t="n"/>
       <c r="D39" s="8" t="n"/>
       <c r="E39" s="5" t="n">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>シリアル送信実装</t>
+          <t>フォトTr配線・遮光チャンバー</t>
         </is>
       </c>
       <c r="G39" s="8" t="n"/>
@@ -1616,11 +1601,11 @@
       <c r="C40" s="9" t="n"/>
       <c r="D40" s="9" t="n"/>
       <c r="E40" s="5" t="n">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>楽譜配列作成・5パート</t>
+          <t>センサーISR実装</t>
         </is>
       </c>
       <c r="G40" s="9" t="n"/>
@@ -1628,27 +1613,17 @@
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="8" t="n"/>
       <c r="B41" s="8" t="n"/>
-      <c r="C41" s="3" t="n">
-        <v>240</v>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>担当D実装（音響合成）</t>
-        </is>
-      </c>
+      <c r="C41" s="9" t="n"/>
+      <c r="D41" s="9" t="n"/>
       <c r="E41" s="5" t="n">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>シリアル受信処理実装</t>
-        </is>
-      </c>
-      <c r="G41" s="13" t="inlineStr">
-        <is>
-          <t>中村・尾添</t>
-        </is>
-      </c>
+          <t>テンポ推定実装</t>
+        </is>
+      </c>
+      <c r="G41" s="9" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="8" t="n"/>
@@ -1656,11 +1631,11 @@
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="n"/>
       <c r="E42" s="5" t="n">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>音色合成エンジン実装</t>
+          <t>状態機械実装</t>
         </is>
       </c>
       <c r="G42" s="8" t="n"/>
@@ -1671,11 +1646,11 @@
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="8" t="n"/>
       <c r="E43" s="5" t="n">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>エフェクト・フェルマータ延奏実装</t>
+          <t>INSTRUMENT_ID輝度キュー実装</t>
         </is>
       </c>
       <c r="G43" s="8" t="n"/>
@@ -1686,60 +1661,44 @@
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="n"/>
       <c r="E44" s="5" t="n">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>音色定義データ作成</t>
+          <t>シリアル通信実装（担当C向け）</t>
         </is>
       </c>
       <c r="G44" s="8" t="n"/>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="9" t="n"/>
-      <c r="B45" s="9" t="n"/>
+      <c r="A45" s="8" t="n"/>
+      <c r="B45" s="8" t="n"/>
       <c r="C45" s="9" t="n"/>
       <c r="D45" s="9" t="n"/>
       <c r="E45" s="5" t="n">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>ADSRパラメータ調整</t>
+          <t>拍検出・オフセット実装</t>
         </is>
       </c>
       <c r="G45" s="9" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>テストフェーズ</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="n">
-        <v>310</v>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>事前確認テスト（P1-P6）</t>
-        </is>
-      </c>
+      <c r="A46" s="8" t="n"/>
+      <c r="B46" s="8" t="n"/>
+      <c r="C46" s="8" t="n"/>
+      <c r="D46" s="8" t="n"/>
       <c r="E46" s="5" t="n">
-        <v>311</v>
+        <v>232</v>
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>赤外線センサー精度確認</t>
-        </is>
-      </c>
-      <c r="G46" s="11" t="inlineStr">
-        <is>
-          <t>長野・慶田</t>
-        </is>
-      </c>
+          <t>楽譜進行制御実装</t>
+        </is>
+      </c>
+      <c r="G46" s="8" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="8" t="n"/>
@@ -1747,19 +1706,14 @@
       <c r="C47" s="8" t="n"/>
       <c r="D47" s="8" t="n"/>
       <c r="E47" s="5" t="n">
-        <v>312</v>
+        <v>233</v>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>フォトTr検出距離確認</t>
-        </is>
-      </c>
-      <c r="G47" s="10" t="inlineStr">
-        <is>
-          <t>長見・飛田
-長野・慶田</t>
-        </is>
-      </c>
+          <t>シリアル送信実装</t>
+        </is>
+      </c>
+      <c r="G47" s="9" t="n"/>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="8" t="n"/>
@@ -1767,11 +1721,11 @@
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="8" t="n"/>
       <c r="E48" s="5" t="n">
-        <v>313</v>
+        <v>234</v>
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>LED輝度・フォトTr検出確認</t>
+          <t>楽譜配列作成・5パート</t>
         </is>
       </c>
       <c r="G48" s="9" t="n"/>
@@ -1782,16 +1736,16 @@
       <c r="C49" s="8" t="n"/>
       <c r="D49" s="8" t="n"/>
       <c r="E49" s="5" t="n">
-        <v>314</v>
+        <v>241</v>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>サーボ動作角度確認</t>
-        </is>
-      </c>
-      <c r="G49" s="10" t="inlineStr">
-        <is>
-          <t>長見・飛田</t>
+          <t>シリアル受信処理実装</t>
+        </is>
+      </c>
+      <c r="G49" s="13" t="inlineStr">
+        <is>
+          <t>中村・尾添</t>
         </is>
       </c>
     </row>
@@ -1801,11 +1755,11 @@
       <c r="C50" s="8" t="n"/>
       <c r="D50" s="8" t="n"/>
       <c r="E50" s="5" t="n">
-        <v>315</v>
+        <v>242</v>
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>サーボ最大BPM確認</t>
+          <t>音色合成エンジン実装</t>
         </is>
       </c>
       <c r="G50" s="9" t="n"/>
@@ -1813,47 +1767,32 @@
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="8" t="n"/>
       <c r="B51" s="8" t="n"/>
-      <c r="C51" s="9" t="n"/>
-      <c r="D51" s="9" t="n"/>
+      <c r="C51" s="8" t="n"/>
+      <c r="D51" s="8" t="n"/>
       <c r="E51" s="5" t="n">
-        <v>316</v>
+        <v>243</v>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>Arduino-Processing通信確認</t>
-        </is>
-      </c>
-      <c r="G51" s="11" t="inlineStr">
-        <is>
-          <t>長野・長山・慶田
-中村・尾添</t>
-        </is>
-      </c>
+          <t>エフェクト・フェルマータ延奏実装</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="n"/>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="8" t="n"/>
       <c r="B52" s="8" t="n"/>
-      <c r="C52" s="3" t="n">
-        <v>320</v>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>単体テスト（U1-U4）</t>
-        </is>
-      </c>
+      <c r="C52" s="8" t="n"/>
+      <c r="D52" s="8" t="n"/>
       <c r="E52" s="5" t="n">
-        <v>321</v>
+        <v>244</v>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>センサーISR・テンポ推定単体テスト</t>
-        </is>
-      </c>
-      <c r="G52" s="11" t="inlineStr">
-        <is>
-          <t>長野・慶田</t>
-        </is>
-      </c>
+          <t>音色定義データ作成</t>
+        </is>
+      </c>
+      <c r="G52" s="9" t="n"/>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="8" t="n"/>
@@ -1861,11 +1800,11 @@
       <c r="C53" s="8" t="n"/>
       <c r="D53" s="8" t="n"/>
       <c r="E53" s="5" t="n">
-        <v>322</v>
+        <v>245</v>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>状態機械単体テスト</t>
+          <t>ADSRパラメータ調整</t>
         </is>
       </c>
       <c r="G53" s="9" t="n"/>
@@ -1876,63 +1815,53 @@
       <c r="C54" s="8" t="n"/>
       <c r="D54" s="8" t="n"/>
       <c r="E54" s="5" t="n">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>楽譜進行・シリアル送信単体テスト</t>
-        </is>
-      </c>
-      <c r="G54" s="12" t="inlineStr">
-        <is>
-          <t>長山・慶田</t>
+          <t>赤外線センサー精度確認</t>
+        </is>
+      </c>
+      <c r="G54" s="11" t="inlineStr">
+        <is>
+          <t>長野・慶田</t>
         </is>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="8" t="n"/>
       <c r="B55" s="8" t="n"/>
-      <c r="C55" s="9" t="n"/>
-      <c r="D55" s="9" t="n"/>
+      <c r="C55" s="8" t="n"/>
+      <c r="D55" s="8" t="n"/>
       <c r="E55" s="5" t="n">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>音色合成・エフェクト単体テスト</t>
-        </is>
-      </c>
-      <c r="G55" s="13" t="inlineStr">
-        <is>
-          <t>中村・尾添</t>
+          <t>フォトTr検出距離確認</t>
+        </is>
+      </c>
+      <c r="G55" s="10" t="inlineStr">
+        <is>
+          <t>長見・飛田
+長野・慶田</t>
         </is>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="8" t="n"/>
       <c r="B56" s="8" t="n"/>
-      <c r="C56" s="3" t="n">
-        <v>330</v>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>結合テスト（C1-C3）</t>
-        </is>
-      </c>
+      <c r="C56" s="8" t="n"/>
+      <c r="D56" s="8" t="n"/>
       <c r="E56" s="5" t="n">
-        <v>331</v>
+        <v>313</v>
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>Arduino-Processing遅延測定</t>
-        </is>
-      </c>
-      <c r="G56" s="11" t="inlineStr">
-        <is>
-          <t>長野・長山・慶田
-中村・尾添</t>
-        </is>
-      </c>
+          <t>LED輝度・フォトTr検出確認</t>
+        </is>
+      </c>
+      <c r="G56" s="9" t="n"/>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="8" t="n"/>
@@ -1940,61 +1869,51 @@
       <c r="C57" s="8" t="n"/>
       <c r="D57" s="8" t="n"/>
       <c r="E57" s="5" t="n">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>同期・テンポ追従確認</t>
-        </is>
-      </c>
-      <c r="G57" s="11" t="inlineStr">
-        <is>
-          <t>長野・長山・慶田</t>
+          <t>サーボ動作角度確認</t>
+        </is>
+      </c>
+      <c r="G57" s="10" t="inlineStr">
+        <is>
+          <t>長見・飛田</t>
         </is>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="8" t="n"/>
       <c r="B58" s="8" t="n"/>
-      <c r="C58" s="9" t="n"/>
-      <c r="D58" s="9" t="n"/>
+      <c r="C58" s="8" t="n"/>
+      <c r="D58" s="8" t="n"/>
       <c r="E58" s="5" t="n">
-        <v>333</v>
+        <v>315</v>
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>フェルマータ動作確認</t>
-        </is>
-      </c>
-      <c r="G58" s="11" t="inlineStr">
-        <is>
-          <t>長野・長山・慶田
-中村・尾添</t>
-        </is>
-      </c>
+          <t>サーボ最大BPM確認</t>
+        </is>
+      </c>
+      <c r="G58" s="9" t="n"/>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="8" t="n"/>
       <c r="B59" s="8" t="n"/>
-      <c r="C59" s="3" t="n">
-        <v>340</v>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>システムテスト（S1-S3）</t>
-        </is>
-      </c>
+      <c r="C59" s="9" t="n"/>
+      <c r="D59" s="9" t="n"/>
       <c r="E59" s="5" t="n">
-        <v>341</v>
+        <v>316</v>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>通し演奏テスト</t>
-        </is>
-      </c>
-      <c r="G59" s="7" t="inlineStr">
-        <is>
-          <t>全員</t>
+          <t>Arduino-Processing通信確認</t>
+        </is>
+      </c>
+      <c r="G59" s="11" t="inlineStr">
+        <is>
+          <t>長野・長山・慶田
+中村・尾添</t>
         </is>
       </c>
     </row>
@@ -2004,29 +1923,187 @@
       <c r="C60" s="8" t="n"/>
       <c r="D60" s="8" t="n"/>
       <c r="E60" s="5" t="n">
-        <v>342</v>
+        <v>321</v>
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>拍タイミング精度評価</t>
+          <t>センサーISR・テンポ推定単体テスト</t>
         </is>
       </c>
       <c r="G60" s="8" t="n"/>
     </row>
     <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="9" t="n"/>
-      <c r="B61" s="9" t="n"/>
+      <c r="A61" s="8" t="n"/>
+      <c r="B61" s="8" t="n"/>
       <c r="C61" s="9" t="n"/>
       <c r="D61" s="9" t="n"/>
       <c r="E61" s="5" t="n">
+        <v>322</v>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>状態機械単体テスト</t>
+        </is>
+      </c>
+      <c r="G61" s="9" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="n"/>
+      <c r="B62" s="8" t="n"/>
+      <c r="C62" s="8" t="n"/>
+      <c r="D62" s="8" t="n"/>
+      <c r="E62" s="5" t="n">
+        <v>323</v>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>楽譜進行・シリアル送信単体テスト</t>
+        </is>
+      </c>
+      <c r="G62" s="12" t="inlineStr">
+        <is>
+          <t>長山・慶田</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="n"/>
+      <c r="B63" s="8" t="n"/>
+      <c r="C63" s="9" t="n"/>
+      <c r="D63" s="9" t="n"/>
+      <c r="E63" s="5" t="n">
+        <v>324</v>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>音色合成・エフェクト単体テスト</t>
+        </is>
+      </c>
+      <c r="G63" s="13" t="inlineStr">
+        <is>
+          <t>中村・尾添</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="n"/>
+      <c r="B64" s="8" t="n"/>
+      <c r="C64" s="3" t="n">
+        <v>330</v>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>結合テスト（C1-C3）</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>331</v>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>Arduino-Processing遅延測定</t>
+        </is>
+      </c>
+      <c r="G64" s="11" t="inlineStr">
+        <is>
+          <t>長野・長山・慶田
+中村・尾添</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="n"/>
+      <c r="B65" s="8" t="n"/>
+      <c r="C65" s="8" t="n"/>
+      <c r="D65" s="8" t="n"/>
+      <c r="E65" s="5" t="n">
+        <v>332</v>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>同期・テンポ追従確認</t>
+        </is>
+      </c>
+      <c r="G65" s="11" t="inlineStr">
+        <is>
+          <t>長野・長山・慶田</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="n"/>
+      <c r="B66" s="8" t="n"/>
+      <c r="C66" s="9" t="n"/>
+      <c r="D66" s="9" t="n"/>
+      <c r="E66" s="5" t="n">
+        <v>333</v>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>フェルマータ動作確認</t>
+        </is>
+      </c>
+      <c r="G66" s="11" t="inlineStr">
+        <is>
+          <t>長野・長山・慶田
+中村・尾添</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="n"/>
+      <c r="B67" s="8" t="n"/>
+      <c r="C67" s="3" t="n">
+        <v>340</v>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>システムテスト（S1-S3）</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>341</v>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>通し演奏テスト</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>全員</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="n"/>
+      <c r="B68" s="8" t="n"/>
+      <c r="C68" s="8" t="n"/>
+      <c r="D68" s="8" t="n"/>
+      <c r="E68" s="5" t="n">
+        <v>342</v>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>拍タイミング精度評価</t>
+        </is>
+      </c>
+      <c r="G68" s="8" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="n"/>
+      <c r="B69" s="9" t="n"/>
+      <c r="C69" s="9" t="n"/>
+      <c r="D69" s="9" t="n"/>
+      <c r="E69" s="5" t="n">
         <v>343</v>
       </c>
-      <c r="F61" s="6" t="inlineStr">
+      <c r="F69" s="6" t="inlineStr">
         <is>
           <t>テンポ変化・フェルマータ完全確認</t>
         </is>
       </c>
-      <c r="G61" s="9" t="n"/>
+      <c r="G69" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="45">
@@ -2086,7 +2163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M79"/>
+  <dimension ref="A1:M87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2094,7 +2171,7 @@
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="7.5" customWidth="1" min="8" max="8"/>
     <col width="7.5" customWidth="1" min="9" max="9"/>
@@ -2491,16 +2568,10 @@
       <c r="M14" s="37" t="inlineStr"/>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="23" t="inlineStr"/>
-      <c r="B15" s="24" t="inlineStr"/>
-      <c r="C15" s="25" t="n">
-        <v>130</v>
-      </c>
-      <c r="D15" s="26" t="inlineStr">
-        <is>
-          <t>担当B設計（センサー・観測）</t>
-        </is>
-      </c>
+      <c r="A15" s="47" t="n"/>
+      <c r="B15" s="48" t="n"/>
+      <c r="C15" s="49" t="n"/>
+      <c r="D15" s="32" t="n"/>
       <c r="E15" s="27" t="n"/>
       <c r="F15" s="27" t="n"/>
       <c r="G15" s="27" t="n"/>
@@ -2517,49 +2588,45 @@
       <c r="C16" s="49" t="n"/>
       <c r="D16" s="32" t="n"/>
       <c r="E16" s="49" t="n">
-        <v>131</v>
-      </c>
-      <c r="F16" s="32" t="inlineStr">
-        <is>
-          <t>赤外線センサー配線設計</t>
+        <v>128</v>
+      </c>
+      <c r="F16" s="65" t="inlineStr">
+        <is>
+          <t>シリアル通信コマンド設計（INSTRUMENT/BPM）</t>
         </is>
       </c>
       <c r="G16" s="33" t="inlineStr">
         <is>
-          <t>長野・慶田</t>
-        </is>
-      </c>
-      <c r="H16" s="34" t="inlineStr"/>
-      <c r="I16" s="50" t="inlineStr"/>
-      <c r="J16" s="35" t="inlineStr"/>
-      <c r="K16" s="35" t="inlineStr"/>
-      <c r="L16" s="35" t="inlineStr"/>
-      <c r="M16" s="37" t="inlineStr"/>
+          <t>長見・飛田</t>
+        </is>
+      </c>
+      <c r="H16" s="34" t="n"/>
+      <c r="I16" s="50" t="n"/>
+      <c r="J16" s="35" t="n"/>
+      <c r="K16" s="35" t="n"/>
+      <c r="L16" s="35" t="n"/>
+      <c r="M16" s="37" t="n"/>
     </row>
     <row r="17" ht="14" customHeight="1">
-      <c r="A17" s="47" t="n"/>
-      <c r="B17" s="48" t="n"/>
-      <c r="C17" s="49" t="n"/>
-      <c r="D17" s="32" t="n"/>
-      <c r="E17" s="49" t="n">
-        <v>132</v>
-      </c>
-      <c r="F17" s="32" t="inlineStr">
-        <is>
-          <t>フォトTr配線設計</t>
-        </is>
-      </c>
-      <c r="G17" s="33" t="inlineStr">
-        <is>
-          <t>長野・慶田</t>
-        </is>
-      </c>
-      <c r="H17" s="34" t="inlineStr"/>
-      <c r="I17" s="50" t="inlineStr"/>
-      <c r="J17" s="35" t="inlineStr"/>
-      <c r="K17" s="35" t="inlineStr"/>
-      <c r="L17" s="35" t="inlineStr"/>
-      <c r="M17" s="37" t="inlineStr"/>
+      <c r="A17" s="23" t="inlineStr"/>
+      <c r="B17" s="24" t="inlineStr"/>
+      <c r="C17" s="25" t="n">
+        <v>130</v>
+      </c>
+      <c r="D17" s="26" t="inlineStr">
+        <is>
+          <t>担当B設計（センサー・観測）</t>
+        </is>
+      </c>
+      <c r="E17" s="27" t="n"/>
+      <c r="F17" s="27" t="n"/>
+      <c r="G17" s="27" t="n"/>
+      <c r="H17" s="27" t="n"/>
+      <c r="I17" s="27" t="n"/>
+      <c r="J17" s="27" t="n"/>
+      <c r="K17" s="27" t="n"/>
+      <c r="L17" s="27" t="n"/>
+      <c r="M17" s="28" t="n"/>
     </row>
     <row r="18" ht="14" customHeight="1">
       <c r="A18" s="47" t="n"/>
@@ -2567,11 +2634,11 @@
       <c r="C18" s="49" t="n"/>
       <c r="D18" s="32" t="n"/>
       <c r="E18" s="49" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F18" s="32" t="inlineStr">
         <is>
-          <t>センサーISR設計</t>
+          <t>赤外線センサー配線設計</t>
         </is>
       </c>
       <c r="G18" s="33" t="inlineStr">
@@ -2592,11 +2659,11 @@
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="32" t="n"/>
       <c r="E19" s="49" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F19" s="32" t="inlineStr">
         <is>
-          <t>テンポ推定アルゴリズム設計</t>
+          <t>フォトTr配線設計</t>
         </is>
       </c>
       <c r="G19" s="33" t="inlineStr">
@@ -2617,11 +2684,11 @@
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="32" t="n"/>
       <c r="E20" s="49" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F20" s="32" t="inlineStr">
         <is>
-          <t>状態機械設計</t>
+          <t>センサーISR設計</t>
         </is>
       </c>
       <c r="G20" s="33" t="inlineStr">
@@ -2637,16 +2704,10 @@
       <c r="M20" s="37" t="inlineStr"/>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="23" t="inlineStr"/>
-      <c r="B21" s="24" t="inlineStr"/>
-      <c r="C21" s="25" t="n">
-        <v>140</v>
-      </c>
-      <c r="D21" s="26" t="inlineStr">
-        <is>
-          <t>担当C設計（演奏制御）</t>
-        </is>
-      </c>
+      <c r="A21" s="47" t="n"/>
+      <c r="B21" s="48" t="n"/>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="32" t="n"/>
       <c r="E21" s="27" t="n"/>
       <c r="F21" s="27" t="n"/>
       <c r="G21" s="27" t="n"/>
@@ -2663,16 +2724,16 @@
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="32" t="n"/>
       <c r="E22" s="49" t="n">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="F22" s="32" t="inlineStr">
         <is>
-          <t>拍検出・オフセット設計</t>
+          <t>状態機械設計</t>
         </is>
       </c>
       <c r="G22" s="33" t="inlineStr">
         <is>
-          <t>長山・慶田</t>
+          <t>長野・慶田</t>
         </is>
       </c>
       <c r="H22" s="34" t="inlineStr"/>
@@ -2688,24 +2749,24 @@
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="32" t="n"/>
       <c r="E23" s="49" t="n">
-        <v>142</v>
-      </c>
-      <c r="F23" s="32" t="inlineStr">
-        <is>
-          <t>楽譜進行制御設計</t>
+        <v>136</v>
+      </c>
+      <c r="F23" s="65" t="inlineStr">
+        <is>
+          <t>キャリブレーション手順設計（CALIBRATE状態）</t>
         </is>
       </c>
       <c r="G23" s="33" t="inlineStr">
         <is>
-          <t>長山・慶田</t>
-        </is>
-      </c>
-      <c r="H23" s="34" t="inlineStr"/>
-      <c r="I23" s="50" t="inlineStr"/>
-      <c r="J23" s="35" t="inlineStr"/>
-      <c r="K23" s="35" t="inlineStr"/>
-      <c r="L23" s="35" t="inlineStr"/>
-      <c r="M23" s="37" t="inlineStr"/>
+          <t>長野・慶田</t>
+        </is>
+      </c>
+      <c r="H23" s="34" t="n"/>
+      <c r="I23" s="50" t="n"/>
+      <c r="J23" s="35" t="n"/>
+      <c r="K23" s="35" t="n"/>
+      <c r="L23" s="35" t="n"/>
+      <c r="M23" s="37" t="n"/>
     </row>
     <row r="24" ht="14" customHeight="1">
       <c r="A24" s="47" t="n"/>
@@ -2713,61 +2774,51 @@
       <c r="C24" s="49" t="n"/>
       <c r="D24" s="32" t="n"/>
       <c r="E24" s="49" t="n">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F24" s="32" t="inlineStr">
         <is>
-          <t>シリアル送信プロトコル設計</t>
+          <t>INSTRUMENT_ID輝度キュー設計</t>
         </is>
       </c>
       <c r="G24" s="33" t="inlineStr">
         <is>
-          <t>長山・慶田</t>
-        </is>
-      </c>
-      <c r="H24" s="34" t="inlineStr"/>
-      <c r="I24" s="50" t="inlineStr"/>
-      <c r="J24" s="35" t="inlineStr"/>
-      <c r="K24" s="35" t="inlineStr"/>
-      <c r="L24" s="35" t="inlineStr"/>
-      <c r="M24" s="37" t="inlineStr"/>
+          <t>長野・慶田</t>
+        </is>
+      </c>
+      <c r="H24" s="34" t="n"/>
+      <c r="I24" s="50" t="n"/>
+      <c r="J24" s="35" t="n"/>
+      <c r="K24" s="35" t="n"/>
+      <c r="L24" s="35" t="n"/>
+      <c r="M24" s="37" t="n"/>
     </row>
     <row r="25" ht="14" customHeight="1">
-      <c r="A25" s="47" t="n"/>
-      <c r="B25" s="48" t="n"/>
-      <c r="C25" s="49" t="n"/>
-      <c r="D25" s="32" t="n"/>
-      <c r="E25" s="49" t="n">
-        <v>144</v>
-      </c>
-      <c r="F25" s="32" t="inlineStr">
-        <is>
-          <t>楽譜配列定義・5パート</t>
-        </is>
-      </c>
-      <c r="G25" s="33" t="inlineStr">
-        <is>
-          <t>長山・慶田</t>
-        </is>
-      </c>
-      <c r="H25" s="34" t="inlineStr"/>
-      <c r="I25" s="50" t="inlineStr"/>
-      <c r="J25" s="35" t="inlineStr"/>
-      <c r="K25" s="35" t="inlineStr"/>
-      <c r="L25" s="35" t="inlineStr"/>
-      <c r="M25" s="37" t="inlineStr"/>
+      <c r="A25" s="23" t="inlineStr"/>
+      <c r="B25" s="24" t="inlineStr"/>
+      <c r="C25" s="25" t="n">
+        <v>140</v>
+      </c>
+      <c r="D25" s="26" t="inlineStr">
+        <is>
+          <t>担当C設計（演奏制御）</t>
+        </is>
+      </c>
+      <c r="E25" s="27" t="n"/>
+      <c r="F25" s="27" t="n"/>
+      <c r="G25" s="27" t="n"/>
+      <c r="H25" s="27" t="n"/>
+      <c r="I25" s="27" t="n"/>
+      <c r="J25" s="27" t="n"/>
+      <c r="K25" s="27" t="n"/>
+      <c r="L25" s="27" t="n"/>
+      <c r="M25" s="28" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="23" t="inlineStr"/>
-      <c r="B26" s="24" t="inlineStr"/>
-      <c r="C26" s="25" t="n">
-        <v>150</v>
-      </c>
-      <c r="D26" s="26" t="inlineStr">
-        <is>
-          <t>担当D設計（音響合成）</t>
-        </is>
-      </c>
+      <c r="A26" s="47" t="n"/>
+      <c r="B26" s="48" t="n"/>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="32" t="n"/>
       <c r="E26" s="27" t="n"/>
       <c r="F26" s="27" t="n"/>
       <c r="G26" s="27" t="n"/>
@@ -2784,16 +2835,16 @@
       <c r="C27" s="49" t="n"/>
       <c r="D27" s="32" t="n"/>
       <c r="E27" s="49" t="n">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="F27" s="32" t="inlineStr">
         <is>
-          <t>シリアル受信処理設計</t>
+          <t>楽譜進行制御設計</t>
         </is>
       </c>
       <c r="G27" s="33" t="inlineStr">
         <is>
-          <t>中村・尾添</t>
+          <t>長山・慶田</t>
         </is>
       </c>
       <c r="H27" s="34" t="inlineStr"/>
@@ -2809,16 +2860,16 @@
       <c r="C28" s="49" t="n"/>
       <c r="D28" s="32" t="n"/>
       <c r="E28" s="49" t="n">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="F28" s="32" t="inlineStr">
         <is>
-          <t>音色合成エンジン設計</t>
+          <t>シリアル送信プロトコル設計</t>
         </is>
       </c>
       <c r="G28" s="33" t="inlineStr">
         <is>
-          <t>中村・尾添</t>
+          <t>長山・慶田</t>
         </is>
       </c>
       <c r="H28" s="34" t="inlineStr"/>
@@ -2834,16 +2885,16 @@
       <c r="C29" s="49" t="n"/>
       <c r="D29" s="32" t="n"/>
       <c r="E29" s="49" t="n">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="F29" s="32" t="inlineStr">
         <is>
-          <t>エフェクト・フェルマータ延奏設計</t>
+          <t>楽譜配列定義・5パート</t>
         </is>
       </c>
       <c r="G29" s="33" t="inlineStr">
         <is>
-          <t>中村・尾添</t>
+          <t>長山・慶田</t>
         </is>
       </c>
       <c r="H29" s="34" t="inlineStr"/>
@@ -2854,29 +2905,25 @@
       <c r="M29" s="37" t="inlineStr"/>
     </row>
     <row r="30" ht="14" customHeight="1">
-      <c r="A30" s="47" t="n"/>
-      <c r="B30" s="48" t="n"/>
-      <c r="C30" s="49" t="n"/>
-      <c r="D30" s="32" t="n"/>
-      <c r="E30" s="49" t="n">
-        <v>154</v>
-      </c>
-      <c r="F30" s="32" t="inlineStr">
-        <is>
-          <t>音色定義シート作成</t>
-        </is>
-      </c>
-      <c r="G30" s="33" t="inlineStr">
-        <is>
-          <t>中村・尾添</t>
-        </is>
-      </c>
-      <c r="H30" s="34" t="inlineStr"/>
-      <c r="I30" s="50" t="inlineStr"/>
-      <c r="J30" s="35" t="inlineStr"/>
-      <c r="K30" s="35" t="inlineStr"/>
-      <c r="L30" s="35" t="inlineStr"/>
-      <c r="M30" s="37" t="inlineStr"/>
+      <c r="A30" s="23" t="inlineStr"/>
+      <c r="B30" s="24" t="inlineStr"/>
+      <c r="C30" s="25" t="n">
+        <v>150</v>
+      </c>
+      <c r="D30" s="26" t="inlineStr">
+        <is>
+          <t>担当D設計（音響合成）</t>
+        </is>
+      </c>
+      <c r="E30" s="27" t="n"/>
+      <c r="F30" s="27" t="n"/>
+      <c r="G30" s="27" t="n"/>
+      <c r="H30" s="27" t="n"/>
+      <c r="I30" s="27" t="n"/>
+      <c r="J30" s="27" t="n"/>
+      <c r="K30" s="27" t="n"/>
+      <c r="L30" s="27" t="n"/>
+      <c r="M30" s="28" t="n"/>
     </row>
     <row r="31" ht="14" customHeight="1">
       <c r="A31" s="47" t="n"/>
@@ -2884,11 +2931,11 @@
       <c r="C31" s="49" t="n"/>
       <c r="D31" s="32" t="n"/>
       <c r="E31" s="49" t="n">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F31" s="32" t="inlineStr">
         <is>
-          <t>ADSRパラメータ仕様策定</t>
+          <t>シリアル受信処理設計</t>
         </is>
       </c>
       <c r="G31" s="33" t="inlineStr">
@@ -2904,37 +2951,25 @@
       <c r="M31" s="37" t="inlineStr"/>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="18" t="n">
-        <v>200</v>
-      </c>
-      <c r="B32" s="19" t="inlineStr">
-        <is>
-          <t>実装フェーズ</t>
-        </is>
-      </c>
-      <c r="C32" s="20" t="n"/>
-      <c r="D32" s="20" t="n"/>
-      <c r="E32" s="20" t="n"/>
-      <c r="F32" s="20" t="n"/>
-      <c r="G32" s="20" t="n"/>
-      <c r="H32" s="20" t="n"/>
-      <c r="I32" s="20" t="n"/>
-      <c r="J32" s="20" t="n"/>
-      <c r="K32" s="20" t="n"/>
-      <c r="L32" s="20" t="n"/>
-      <c r="M32" s="21" t="n"/>
+      <c r="A32" s="47" t="n"/>
+      <c r="B32" s="48" t="n"/>
+      <c r="C32" s="27" t="n"/>
+      <c r="D32" s="27" t="n"/>
+      <c r="E32" s="27" t="n"/>
+      <c r="F32" s="27" t="n"/>
+      <c r="G32" s="27" t="n"/>
+      <c r="H32" s="27" t="n"/>
+      <c r="I32" s="27" t="n"/>
+      <c r="J32" s="27" t="n"/>
+      <c r="K32" s="27" t="n"/>
+      <c r="L32" s="27" t="n"/>
+      <c r="M32" s="28" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="23" t="inlineStr"/>
-      <c r="B33" s="24" t="inlineStr"/>
-      <c r="C33" s="25" t="n">
-        <v>210</v>
-      </c>
-      <c r="D33" s="26" t="inlineStr">
-        <is>
-          <t>担当A実装（指揮者人形ユニット）</t>
-        </is>
-      </c>
+      <c r="A33" s="47" t="n"/>
+      <c r="B33" s="48" t="n"/>
+      <c r="C33" s="49" t="n"/>
+      <c r="D33" s="32" t="n"/>
       <c r="E33" s="27" t="n"/>
       <c r="F33" s="27" t="n"/>
       <c r="G33" s="27" t="n"/>
@@ -2951,19 +2986,19 @@
       <c r="C34" s="49" t="n"/>
       <c r="D34" s="32" t="n"/>
       <c r="E34" s="49" t="n">
-        <v>211</v>
+        <v>154</v>
       </c>
       <c r="F34" s="32" t="inlineStr">
         <is>
-          <t>サーボ機構組み立て</t>
+          <t>音色定義シート作成</t>
         </is>
       </c>
       <c r="G34" s="33" t="inlineStr">
         <is>
-          <t>長見・飛田</t>
-        </is>
-      </c>
-      <c r="H34" s="51" t="inlineStr"/>
+          <t>中村・尾添</t>
+        </is>
+      </c>
+      <c r="H34" s="34" t="inlineStr"/>
       <c r="I34" s="50" t="inlineStr"/>
       <c r="J34" s="35" t="inlineStr"/>
       <c r="K34" s="35" t="inlineStr"/>
@@ -2976,19 +3011,19 @@
       <c r="C35" s="49" t="n"/>
       <c r="D35" s="32" t="n"/>
       <c r="E35" s="49" t="n">
-        <v>212</v>
+        <v>155</v>
       </c>
       <c r="F35" s="32" t="inlineStr">
         <is>
-          <t>腕・反射板取り付け</t>
+          <t>ADSRパラメータ仕様策定</t>
         </is>
       </c>
       <c r="G35" s="33" t="inlineStr">
         <is>
-          <t>長見・飛田</t>
-        </is>
-      </c>
-      <c r="H35" s="51" t="inlineStr"/>
+          <t>中村・尾添</t>
+        </is>
+      </c>
+      <c r="H35" s="34" t="inlineStr"/>
       <c r="I35" s="50" t="inlineStr"/>
       <c r="J35" s="35" t="inlineStr"/>
       <c r="K35" s="35" t="inlineStr"/>
@@ -2996,54 +3031,46 @@
       <c r="M35" s="37" t="inlineStr"/>
     </row>
     <row r="36" ht="14" customHeight="1">
-      <c r="A36" s="47" t="n"/>
-      <c r="B36" s="48" t="n"/>
-      <c r="C36" s="49" t="n"/>
-      <c r="D36" s="32" t="n"/>
-      <c r="E36" s="49" t="n">
-        <v>213</v>
-      </c>
-      <c r="F36" s="32" t="inlineStr">
-        <is>
-          <t>LED駆動回路配線</t>
-        </is>
-      </c>
-      <c r="G36" s="33" t="inlineStr">
-        <is>
-          <t>長見・飛田</t>
-        </is>
-      </c>
-      <c r="H36" s="51" t="inlineStr"/>
-      <c r="I36" s="50" t="inlineStr"/>
-      <c r="J36" s="35" t="inlineStr"/>
-      <c r="K36" s="35" t="inlineStr"/>
-      <c r="L36" s="35" t="inlineStr"/>
-      <c r="M36" s="37" t="inlineStr"/>
+      <c r="A36" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="B36" s="19" t="inlineStr">
+        <is>
+          <t>実装フェーズ</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="n"/>
+      <c r="D36" s="20" t="n"/>
+      <c r="E36" s="20" t="n"/>
+      <c r="F36" s="20" t="n"/>
+      <c r="G36" s="20" t="n"/>
+      <c r="H36" s="20" t="n"/>
+      <c r="I36" s="20" t="n"/>
+      <c r="J36" s="20" t="n"/>
+      <c r="K36" s="20" t="n"/>
+      <c r="L36" s="20" t="n"/>
+      <c r="M36" s="21" t="n"/>
     </row>
     <row r="37" ht="14" customHeight="1">
-      <c r="A37" s="47" t="n"/>
-      <c r="B37" s="48" t="n"/>
-      <c r="C37" s="49" t="n"/>
-      <c r="D37" s="32" t="n"/>
-      <c r="E37" s="49" t="n">
-        <v>214</v>
-      </c>
-      <c r="F37" s="32" t="inlineStr">
-        <is>
-          <t>サーボ駆動回路配線</t>
-        </is>
-      </c>
-      <c r="G37" s="33" t="inlineStr">
-        <is>
-          <t>長見・飛田</t>
-        </is>
-      </c>
-      <c r="H37" s="34" t="inlineStr"/>
-      <c r="I37" s="50" t="inlineStr"/>
-      <c r="J37" s="38" t="inlineStr"/>
-      <c r="K37" s="35" t="inlineStr"/>
-      <c r="L37" s="35" t="inlineStr"/>
-      <c r="M37" s="37" t="inlineStr"/>
+      <c r="A37" s="23" t="inlineStr"/>
+      <c r="B37" s="24" t="inlineStr"/>
+      <c r="C37" s="25" t="n">
+        <v>210</v>
+      </c>
+      <c r="D37" s="26" t="inlineStr">
+        <is>
+          <t>担当A実装（指揮者人形ユニット）</t>
+        </is>
+      </c>
+      <c r="E37" s="27" t="n"/>
+      <c r="F37" s="27" t="n"/>
+      <c r="G37" s="27" t="n"/>
+      <c r="H37" s="27" t="n"/>
+      <c r="I37" s="27" t="n"/>
+      <c r="J37" s="27" t="n"/>
+      <c r="K37" s="27" t="n"/>
+      <c r="L37" s="27" t="n"/>
+      <c r="M37" s="28" t="n"/>
     </row>
     <row r="38" ht="14" customHeight="1">
       <c r="A38" s="47" t="n"/>
@@ -3051,11 +3078,11 @@
       <c r="C38" s="49" t="n"/>
       <c r="D38" s="32" t="n"/>
       <c r="E38" s="49" t="n">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="F38" s="32" t="inlineStr">
         <is>
-          <t>サーボ制御SW実装</t>
+          <t>サーボ機構組み立て</t>
         </is>
       </c>
       <c r="G38" s="33" t="inlineStr">
@@ -3063,10 +3090,10 @@
           <t>長見・飛田</t>
         </is>
       </c>
-      <c r="H38" s="34" t="inlineStr"/>
+      <c r="H38" s="61" t="inlineStr"/>
       <c r="I38" s="50" t="inlineStr"/>
-      <c r="J38" s="38" t="inlineStr"/>
-      <c r="K38" s="35" t="inlineStr"/>
+      <c r="J38" s="35" t="inlineStr"/>
+      <c r="K38" s="38" t="inlineStr"/>
       <c r="L38" s="35" t="inlineStr"/>
       <c r="M38" s="37" t="inlineStr"/>
     </row>
@@ -3076,11 +3103,11 @@
       <c r="C39" s="49" t="n"/>
       <c r="D39" s="32" t="n"/>
       <c r="E39" s="49" t="n">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="F39" s="32" t="inlineStr">
         <is>
-          <t>輝度エンコードLED制御SW実装</t>
+          <t>腕・反射板取り付け</t>
         </is>
       </c>
       <c r="G39" s="33" t="inlineStr">
@@ -3088,24 +3115,18 @@
           <t>長見・飛田</t>
         </is>
       </c>
-      <c r="H39" s="34" t="inlineStr"/>
+      <c r="H39" s="61" t="inlineStr"/>
       <c r="I39" s="50" t="inlineStr"/>
-      <c r="J39" s="38" t="inlineStr"/>
-      <c r="K39" s="35" t="inlineStr"/>
+      <c r="J39" s="35" t="inlineStr"/>
+      <c r="K39" s="38" t="inlineStr"/>
       <c r="L39" s="35" t="inlineStr"/>
       <c r="M39" s="37" t="inlineStr"/>
     </row>
     <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="23" t="inlineStr"/>
-      <c r="B40" s="24" t="inlineStr"/>
-      <c r="C40" s="25" t="n">
-        <v>220</v>
-      </c>
-      <c r="D40" s="26" t="inlineStr">
-        <is>
-          <t>担当B実装（センサー・観測）</t>
-        </is>
-      </c>
+      <c r="A40" s="47" t="n"/>
+      <c r="B40" s="48" t="n"/>
+      <c r="C40" s="49" t="n"/>
+      <c r="D40" s="32" t="n"/>
       <c r="E40" s="27" t="n"/>
       <c r="F40" s="27" t="n"/>
       <c r="G40" s="27" t="n"/>
@@ -3122,22 +3143,22 @@
       <c r="C41" s="49" t="n"/>
       <c r="D41" s="32" t="n"/>
       <c r="E41" s="49" t="n">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="F41" s="32" t="inlineStr">
         <is>
-          <t>赤外線センサー配線</t>
+          <t>サーボ駆動回路配線</t>
         </is>
       </c>
       <c r="G41" s="33" t="inlineStr">
         <is>
-          <t>長野・慶田</t>
-        </is>
-      </c>
-      <c r="H41" s="52" t="inlineStr"/>
+          <t>長見・飛田</t>
+        </is>
+      </c>
+      <c r="H41" s="34" t="inlineStr"/>
       <c r="I41" s="50" t="inlineStr"/>
-      <c r="J41" s="35" t="inlineStr"/>
-      <c r="K41" s="35" t="inlineStr"/>
+      <c r="J41" s="62" t="inlineStr"/>
+      <c r="K41" s="38" t="inlineStr"/>
       <c r="L41" s="35" t="inlineStr"/>
       <c r="M41" s="37" t="inlineStr"/>
     </row>
@@ -3147,21 +3168,21 @@
       <c r="C42" s="49" t="n"/>
       <c r="D42" s="32" t="n"/>
       <c r="E42" s="49" t="n">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="F42" s="32" t="inlineStr">
         <is>
-          <t>フォトTr配線・遮光チャンバー</t>
+          <t>サーボ制御SW実装</t>
         </is>
       </c>
       <c r="G42" s="33" t="inlineStr">
         <is>
-          <t>長野・慶田</t>
-        </is>
-      </c>
-      <c r="H42" s="52" t="inlineStr"/>
+          <t>長見・飛田</t>
+        </is>
+      </c>
+      <c r="H42" s="34" t="inlineStr"/>
       <c r="I42" s="50" t="inlineStr"/>
-      <c r="J42" s="35" t="inlineStr"/>
+      <c r="J42" s="38" t="inlineStr"/>
       <c r="K42" s="35" t="inlineStr"/>
       <c r="L42" s="35" t="inlineStr"/>
       <c r="M42" s="37" t="inlineStr"/>
@@ -3172,21 +3193,21 @@
       <c r="C43" s="49" t="n"/>
       <c r="D43" s="32" t="n"/>
       <c r="E43" s="49" t="n">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="F43" s="32" t="inlineStr">
         <is>
-          <t>センサーISR実装</t>
+          <t>輝度エンコードLED制御SW実装</t>
         </is>
       </c>
       <c r="G43" s="33" t="inlineStr">
         <is>
-          <t>長野・慶田</t>
+          <t>長見・飛田</t>
         </is>
       </c>
       <c r="H43" s="34" t="inlineStr"/>
       <c r="I43" s="50" t="inlineStr"/>
-      <c r="J43" s="39" t="inlineStr"/>
+      <c r="J43" s="38" t="inlineStr"/>
       <c r="K43" s="35" t="inlineStr"/>
       <c r="L43" s="35" t="inlineStr"/>
       <c r="M43" s="37" t="inlineStr"/>
@@ -3197,24 +3218,24 @@
       <c r="C44" s="49" t="n"/>
       <c r="D44" s="32" t="n"/>
       <c r="E44" s="49" t="n">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="F44" s="32" t="inlineStr">
         <is>
-          <t>テンポ推定実装</t>
+          <t>Processing GUI実装</t>
         </is>
       </c>
       <c r="G44" s="33" t="inlineStr">
         <is>
-          <t>長野・慶田</t>
-        </is>
-      </c>
-      <c r="H44" s="34" t="inlineStr"/>
-      <c r="I44" s="50" t="inlineStr"/>
-      <c r="J44" s="39" t="inlineStr"/>
-      <c r="K44" s="35" t="inlineStr"/>
-      <c r="L44" s="35" t="inlineStr"/>
-      <c r="M44" s="37" t="inlineStr"/>
+          <t>長見・飛田</t>
+        </is>
+      </c>
+      <c r="H44" s="51" t="n"/>
+      <c r="I44" s="50" t="n"/>
+      <c r="J44" s="63" t="n"/>
+      <c r="K44" s="35" t="n"/>
+      <c r="L44" s="35" t="n"/>
+      <c r="M44" s="37" t="n"/>
     </row>
     <row r="45" ht="14" customHeight="1">
       <c r="A45" s="47" t="n"/>
@@ -3222,34 +3243,34 @@
       <c r="C45" s="49" t="n"/>
       <c r="D45" s="32" t="n"/>
       <c r="E45" s="49" t="n">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F45" s="32" t="inlineStr">
         <is>
-          <t>状態機械実装</t>
+          <t>シリアル通信実装（PC→Arduino）</t>
         </is>
       </c>
       <c r="G45" s="33" t="inlineStr">
         <is>
-          <t>長野・慶田</t>
-        </is>
-      </c>
-      <c r="H45" s="34" t="inlineStr"/>
-      <c r="I45" s="50" t="inlineStr"/>
-      <c r="J45" s="39" t="inlineStr"/>
-      <c r="K45" s="35" t="inlineStr"/>
-      <c r="L45" s="35" t="inlineStr"/>
-      <c r="M45" s="37" t="inlineStr"/>
+          <t>長見・飛田</t>
+        </is>
+      </c>
+      <c r="H45" s="34" t="n"/>
+      <c r="I45" s="50" t="n"/>
+      <c r="J45" s="63" t="n"/>
+      <c r="K45" s="35" t="n"/>
+      <c r="L45" s="35" t="n"/>
+      <c r="M45" s="37" t="n"/>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" s="23" t="inlineStr"/>
       <c r="B46" s="24" t="inlineStr"/>
       <c r="C46" s="25" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="D46" s="26" t="inlineStr">
         <is>
-          <t>担当C実装（演奏制御）</t>
+          <t>担当B実装（センサー・観測）</t>
         </is>
       </c>
       <c r="E46" s="27" t="n"/>
@@ -3268,22 +3289,22 @@
       <c r="C47" s="49" t="n"/>
       <c r="D47" s="32" t="n"/>
       <c r="E47" s="49" t="n">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="F47" s="32" t="inlineStr">
         <is>
-          <t>拍検出・オフセット実装</t>
+          <t>赤外線センサー配線</t>
         </is>
       </c>
       <c r="G47" s="33" t="inlineStr">
         <is>
-          <t>長山・慶田</t>
-        </is>
-      </c>
-      <c r="H47" s="53" t="inlineStr"/>
+          <t>長野・慶田</t>
+        </is>
+      </c>
+      <c r="H47" s="34" t="inlineStr"/>
       <c r="I47" s="50" t="inlineStr"/>
       <c r="J47" s="35" t="inlineStr"/>
-      <c r="K47" s="35" t="inlineStr"/>
+      <c r="K47" s="39" t="inlineStr"/>
       <c r="L47" s="35" t="inlineStr"/>
       <c r="M47" s="37" t="inlineStr"/>
     </row>
@@ -3293,22 +3314,22 @@
       <c r="C48" s="49" t="n"/>
       <c r="D48" s="32" t="n"/>
       <c r="E48" s="49" t="n">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="F48" s="32" t="inlineStr">
         <is>
-          <t>楽譜進行制御実装</t>
+          <t>フォトTr配線・遮光チャンバー</t>
         </is>
       </c>
       <c r="G48" s="33" t="inlineStr">
         <is>
-          <t>長山・慶田</t>
-        </is>
-      </c>
-      <c r="H48" s="53" t="inlineStr"/>
+          <t>長野・慶田</t>
+        </is>
+      </c>
+      <c r="H48" s="34" t="inlineStr"/>
       <c r="I48" s="50" t="inlineStr"/>
       <c r="J48" s="35" t="inlineStr"/>
-      <c r="K48" s="35" t="inlineStr"/>
+      <c r="K48" s="39" t="inlineStr"/>
       <c r="L48" s="35" t="inlineStr"/>
       <c r="M48" s="37" t="inlineStr"/>
     </row>
@@ -3318,21 +3339,21 @@
       <c r="C49" s="49" t="n"/>
       <c r="D49" s="32" t="n"/>
       <c r="E49" s="49" t="n">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="F49" s="32" t="inlineStr">
         <is>
-          <t>シリアル送信実装</t>
+          <t>センサーISR実装</t>
         </is>
       </c>
       <c r="G49" s="33" t="inlineStr">
         <is>
-          <t>長山・慶田</t>
+          <t>長野・慶田</t>
         </is>
       </c>
       <c r="H49" s="34" t="inlineStr"/>
       <c r="I49" s="50" t="inlineStr"/>
-      <c r="J49" s="40" t="inlineStr"/>
+      <c r="J49" s="39" t="inlineStr"/>
       <c r="K49" s="35" t="inlineStr"/>
       <c r="L49" s="35" t="inlineStr"/>
       <c r="M49" s="37" t="inlineStr"/>
@@ -3343,36 +3364,30 @@
       <c r="C50" s="49" t="n"/>
       <c r="D50" s="32" t="n"/>
       <c r="E50" s="49" t="n">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="F50" s="32" t="inlineStr">
         <is>
-          <t>楽譜配列作成・5パート</t>
+          <t>テンポ推定実装</t>
         </is>
       </c>
       <c r="G50" s="33" t="inlineStr">
         <is>
-          <t>長山・慶田</t>
-        </is>
-      </c>
-      <c r="H50" s="34" t="inlineStr"/>
+          <t>長野・慶田</t>
+        </is>
+      </c>
+      <c r="H50" s="52" t="inlineStr"/>
       <c r="I50" s="50" t="inlineStr"/>
-      <c r="J50" s="40" t="inlineStr"/>
-      <c r="K50" s="40" t="inlineStr"/>
+      <c r="J50" s="62" t="inlineStr"/>
+      <c r="K50" s="35" t="inlineStr"/>
       <c r="L50" s="35" t="inlineStr"/>
       <c r="M50" s="37" t="inlineStr"/>
     </row>
     <row r="51" ht="15" customHeight="1">
-      <c r="A51" s="23" t="inlineStr"/>
-      <c r="B51" s="24" t="inlineStr"/>
-      <c r="C51" s="25" t="n">
-        <v>240</v>
-      </c>
-      <c r="D51" s="26" t="inlineStr">
-        <is>
-          <t>担当D実装（音響合成）</t>
-        </is>
-      </c>
+      <c r="A51" s="47" t="n"/>
+      <c r="B51" s="48" t="n"/>
+      <c r="C51" s="49" t="n"/>
+      <c r="D51" s="32" t="n"/>
       <c r="E51" s="27" t="n"/>
       <c r="F51" s="27" t="n"/>
       <c r="G51" s="27" t="n"/>
@@ -3389,24 +3404,24 @@
       <c r="C52" s="49" t="n"/>
       <c r="D52" s="32" t="n"/>
       <c r="E52" s="49" t="n">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F52" s="32" t="inlineStr">
         <is>
-          <t>シリアル受信処理実装</t>
+          <t>INSTRUMENT_ID輝度キュー実装</t>
         </is>
       </c>
       <c r="G52" s="33" t="inlineStr">
         <is>
-          <t>中村・尾添</t>
-        </is>
-      </c>
-      <c r="H52" s="54" t="inlineStr"/>
-      <c r="I52" s="50" t="inlineStr"/>
-      <c r="J52" s="35" t="inlineStr"/>
-      <c r="K52" s="35" t="inlineStr"/>
-      <c r="L52" s="35" t="inlineStr"/>
-      <c r="M52" s="37" t="inlineStr"/>
+          <t>長野・慶田</t>
+        </is>
+      </c>
+      <c r="H52" s="34" t="n"/>
+      <c r="I52" s="50" t="n"/>
+      <c r="J52" s="64" t="n"/>
+      <c r="K52" s="35" t="n"/>
+      <c r="L52" s="35" t="n"/>
+      <c r="M52" s="37" t="n"/>
     </row>
     <row r="53" ht="14" customHeight="1">
       <c r="A53" s="47" t="n"/>
@@ -3414,49 +3429,45 @@
       <c r="C53" s="49" t="n"/>
       <c r="D53" s="32" t="n"/>
       <c r="E53" s="49" t="n">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="F53" s="32" t="inlineStr">
         <is>
-          <t>音色合成エンジン実装</t>
+          <t>シリアル通信実装（担当C向け）</t>
         </is>
       </c>
       <c r="G53" s="33" t="inlineStr">
         <is>
-          <t>中村・尾添</t>
-        </is>
-      </c>
-      <c r="H53" s="54" t="inlineStr"/>
-      <c r="I53" s="50" t="inlineStr"/>
-      <c r="J53" s="41" t="inlineStr"/>
-      <c r="K53" s="35" t="inlineStr"/>
-      <c r="L53" s="35" t="inlineStr"/>
-      <c r="M53" s="37" t="inlineStr"/>
+          <t>長野・慶田</t>
+        </is>
+      </c>
+      <c r="H53" s="34" t="n"/>
+      <c r="I53" s="50" t="n"/>
+      <c r="J53" s="64" t="n"/>
+      <c r="K53" s="35" t="n"/>
+      <c r="L53" s="35" t="n"/>
+      <c r="M53" s="37" t="n"/>
     </row>
     <row r="54" ht="14" customHeight="1">
-      <c r="A54" s="47" t="n"/>
-      <c r="B54" s="48" t="n"/>
-      <c r="C54" s="49" t="n"/>
-      <c r="D54" s="32" t="n"/>
-      <c r="E54" s="49" t="n">
-        <v>243</v>
-      </c>
-      <c r="F54" s="32" t="inlineStr">
-        <is>
-          <t>エフェクト・フェルマータ延奏実装</t>
-        </is>
-      </c>
-      <c r="G54" s="33" t="inlineStr">
-        <is>
-          <t>中村・尾添</t>
-        </is>
-      </c>
-      <c r="H54" s="34" t="inlineStr"/>
-      <c r="I54" s="50" t="inlineStr"/>
-      <c r="J54" s="41" t="inlineStr"/>
-      <c r="K54" s="35" t="inlineStr"/>
-      <c r="L54" s="35" t="inlineStr"/>
-      <c r="M54" s="37" t="inlineStr"/>
+      <c r="A54" s="23" t="inlineStr"/>
+      <c r="B54" s="24" t="inlineStr"/>
+      <c r="C54" s="25" t="n">
+        <v>230</v>
+      </c>
+      <c r="D54" s="26" t="inlineStr">
+        <is>
+          <t>担当C実装（演奏制御）</t>
+        </is>
+      </c>
+      <c r="E54" s="27" t="n"/>
+      <c r="F54" s="27" t="n"/>
+      <c r="G54" s="27" t="n"/>
+      <c r="H54" s="27" t="n"/>
+      <c r="I54" s="27" t="n"/>
+      <c r="J54" s="27" t="n"/>
+      <c r="K54" s="27" t="n"/>
+      <c r="L54" s="27" t="n"/>
+      <c r="M54" s="28" t="n"/>
     </row>
     <row r="55" ht="14" customHeight="1">
       <c r="A55" s="47" t="n"/>
@@ -3464,22 +3475,22 @@
       <c r="C55" s="49" t="n"/>
       <c r="D55" s="32" t="n"/>
       <c r="E55" s="49" t="n">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="F55" s="32" t="inlineStr">
         <is>
-          <t>音色定義データ作成</t>
+          <t>拍検出・オフセット実装</t>
         </is>
       </c>
       <c r="G55" s="33" t="inlineStr">
         <is>
-          <t>中村・尾添</t>
-        </is>
-      </c>
-      <c r="H55" s="34" t="inlineStr"/>
+          <t>長山・慶田</t>
+        </is>
+      </c>
+      <c r="H55" s="61" t="inlineStr"/>
       <c r="I55" s="50" t="inlineStr"/>
-      <c r="J55" s="41" t="inlineStr"/>
-      <c r="K55" s="41" t="inlineStr"/>
+      <c r="J55" s="40" t="inlineStr"/>
+      <c r="K55" s="35" t="inlineStr"/>
       <c r="L55" s="35" t="inlineStr"/>
       <c r="M55" s="37" t="inlineStr"/>
     </row>
@@ -3489,57 +3500,45 @@
       <c r="C56" s="49" t="n"/>
       <c r="D56" s="32" t="n"/>
       <c r="E56" s="49" t="n">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="F56" s="32" t="inlineStr">
         <is>
-          <t>ADSRパラメータ調整</t>
+          <t>楽譜進行制御実装</t>
         </is>
       </c>
       <c r="G56" s="33" t="inlineStr">
         <is>
-          <t>中村・尾添</t>
-        </is>
-      </c>
-      <c r="H56" s="34" t="inlineStr"/>
+          <t>長山・慶田</t>
+        </is>
+      </c>
+      <c r="H56" s="53" t="inlineStr"/>
       <c r="I56" s="50" t="inlineStr"/>
-      <c r="J56" s="35" t="inlineStr"/>
-      <c r="K56" s="41" t="inlineStr"/>
+      <c r="J56" s="40" t="inlineStr"/>
+      <c r="K56" s="35" t="inlineStr"/>
       <c r="L56" s="35" t="inlineStr"/>
       <c r="M56" s="37" t="inlineStr"/>
     </row>
     <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="18" t="n">
-        <v>300</v>
-      </c>
-      <c r="B57" s="19" t="inlineStr">
-        <is>
-          <t>テストフェーズ</t>
-        </is>
-      </c>
-      <c r="C57" s="20" t="n"/>
-      <c r="D57" s="20" t="n"/>
-      <c r="E57" s="20" t="n"/>
-      <c r="F57" s="20" t="n"/>
-      <c r="G57" s="20" t="n"/>
-      <c r="H57" s="20" t="n"/>
-      <c r="I57" s="20" t="n"/>
-      <c r="J57" s="20" t="n"/>
-      <c r="K57" s="20" t="n"/>
-      <c r="L57" s="20" t="n"/>
-      <c r="M57" s="21" t="n"/>
+      <c r="A57" s="47" t="n"/>
+      <c r="B57" s="48" t="n"/>
+      <c r="C57" s="27" t="n"/>
+      <c r="D57" s="27" t="n"/>
+      <c r="E57" s="27" t="n"/>
+      <c r="F57" s="27" t="n"/>
+      <c r="G57" s="27" t="n"/>
+      <c r="H57" s="27" t="n"/>
+      <c r="I57" s="27" t="n"/>
+      <c r="J57" s="27" t="n"/>
+      <c r="K57" s="27" t="n"/>
+      <c r="L57" s="27" t="n"/>
+      <c r="M57" s="28" t="n"/>
     </row>
     <row r="58" ht="15" customHeight="1">
-      <c r="A58" s="23" t="inlineStr"/>
-      <c r="B58" s="24" t="inlineStr"/>
-      <c r="C58" s="25" t="n">
-        <v>310</v>
-      </c>
-      <c r="D58" s="26" t="inlineStr">
-        <is>
-          <t>事前確認テスト（P1-P6）</t>
-        </is>
-      </c>
+      <c r="A58" s="47" t="n"/>
+      <c r="B58" s="48" t="n"/>
+      <c r="C58" s="49" t="n"/>
+      <c r="D58" s="32" t="n"/>
       <c r="E58" s="27" t="n"/>
       <c r="F58" s="27" t="n"/>
       <c r="G58" s="27" t="n"/>
@@ -3551,29 +3550,25 @@
       <c r="M58" s="28" t="n"/>
     </row>
     <row r="59" ht="14" customHeight="1">
-      <c r="A59" s="47" t="n"/>
-      <c r="B59" s="48" t="n"/>
-      <c r="C59" s="49" t="n"/>
-      <c r="D59" s="32" t="n"/>
-      <c r="E59" s="49" t="n">
-        <v>311</v>
-      </c>
-      <c r="F59" s="32" t="inlineStr">
-        <is>
-          <t>赤外線センサー精度確認</t>
-        </is>
-      </c>
-      <c r="G59" s="33" t="inlineStr">
-        <is>
-          <t>長野・慶田</t>
-        </is>
-      </c>
-      <c r="H59" s="34" t="inlineStr"/>
-      <c r="I59" s="50" t="inlineStr"/>
-      <c r="J59" s="35" t="inlineStr"/>
-      <c r="K59" s="42" t="inlineStr"/>
-      <c r="L59" s="35" t="inlineStr"/>
-      <c r="M59" s="37" t="inlineStr"/>
+      <c r="A59" s="23" t="inlineStr"/>
+      <c r="B59" s="24" t="inlineStr"/>
+      <c r="C59" s="25" t="n">
+        <v>240</v>
+      </c>
+      <c r="D59" s="26" t="inlineStr">
+        <is>
+          <t>担当D実装（音響合成）</t>
+        </is>
+      </c>
+      <c r="E59" s="27" t="n"/>
+      <c r="F59" s="27" t="n"/>
+      <c r="G59" s="27" t="n"/>
+      <c r="H59" s="27" t="n"/>
+      <c r="I59" s="27" t="n"/>
+      <c r="J59" s="27" t="n"/>
+      <c r="K59" s="27" t="n"/>
+      <c r="L59" s="27" t="n"/>
+      <c r="M59" s="28" t="n"/>
     </row>
     <row r="60" ht="14" customHeight="1">
       <c r="A60" s="47" t="n"/>
@@ -3581,22 +3576,22 @@
       <c r="C60" s="49" t="n"/>
       <c r="D60" s="32" t="n"/>
       <c r="E60" s="49" t="n">
-        <v>312</v>
+        <v>241</v>
       </c>
       <c r="F60" s="32" t="inlineStr">
         <is>
-          <t>フォトTr検出距離確認</t>
+          <t>シリアル受信処理実装</t>
         </is>
       </c>
       <c r="G60" s="33" t="inlineStr">
         <is>
-          <t>長見・飛田/長野・慶田</t>
-        </is>
-      </c>
-      <c r="H60" s="34" t="inlineStr"/>
+          <t>中村・尾添</t>
+        </is>
+      </c>
+      <c r="H60" s="54" t="inlineStr"/>
       <c r="I60" s="50" t="inlineStr"/>
-      <c r="J60" s="35" t="inlineStr"/>
-      <c r="K60" s="42" t="inlineStr"/>
+      <c r="J60" s="41" t="inlineStr"/>
+      <c r="K60" s="35" t="inlineStr"/>
       <c r="L60" s="35" t="inlineStr"/>
       <c r="M60" s="37" t="inlineStr"/>
     </row>
@@ -3606,22 +3601,22 @@
       <c r="C61" s="49" t="n"/>
       <c r="D61" s="32" t="n"/>
       <c r="E61" s="49" t="n">
-        <v>313</v>
+        <v>242</v>
       </c>
       <c r="F61" s="32" t="inlineStr">
         <is>
-          <t>LED輝度・フォトTr検出確認</t>
+          <t>音色合成エンジン実装</t>
         </is>
       </c>
       <c r="G61" s="33" t="inlineStr">
         <is>
-          <t>長見・飛田/長野・慶田</t>
-        </is>
-      </c>
-      <c r="H61" s="34" t="inlineStr"/>
+          <t>中村・尾添</t>
+        </is>
+      </c>
+      <c r="H61" s="54" t="inlineStr"/>
       <c r="I61" s="50" t="inlineStr"/>
-      <c r="J61" s="35" t="inlineStr"/>
-      <c r="K61" s="42" t="inlineStr"/>
+      <c r="J61" s="41" t="inlineStr"/>
+      <c r="K61" s="35" t="inlineStr"/>
       <c r="L61" s="35" t="inlineStr"/>
       <c r="M61" s="37" t="inlineStr"/>
     </row>
@@ -3631,22 +3626,22 @@
       <c r="C62" s="49" t="n"/>
       <c r="D62" s="32" t="n"/>
       <c r="E62" s="49" t="n">
-        <v>314</v>
+        <v>243</v>
       </c>
       <c r="F62" s="32" t="inlineStr">
         <is>
-          <t>サーボ動作角度確認</t>
+          <t>エフェクト・フェルマータ延奏実装</t>
         </is>
       </c>
       <c r="G62" s="33" t="inlineStr">
         <is>
-          <t>長見・飛田</t>
+          <t>中村・尾添</t>
         </is>
       </c>
       <c r="H62" s="34" t="inlineStr"/>
       <c r="I62" s="50" t="inlineStr"/>
-      <c r="J62" s="35" t="inlineStr"/>
-      <c r="K62" s="42" t="inlineStr"/>
+      <c r="J62" s="41" t="inlineStr"/>
+      <c r="K62" s="35" t="inlineStr"/>
       <c r="L62" s="35" t="inlineStr"/>
       <c r="M62" s="37" t="inlineStr"/>
     </row>
@@ -3656,22 +3651,22 @@
       <c r="C63" s="49" t="n"/>
       <c r="D63" s="32" t="n"/>
       <c r="E63" s="49" t="n">
-        <v>315</v>
+        <v>244</v>
       </c>
       <c r="F63" s="32" t="inlineStr">
         <is>
-          <t>サーボ最大BPM確認</t>
+          <t>音色定義データ作成</t>
         </is>
       </c>
       <c r="G63" s="33" t="inlineStr">
         <is>
-          <t>長見・飛田</t>
+          <t>中村・尾添</t>
         </is>
       </c>
       <c r="H63" s="34" t="inlineStr"/>
       <c r="I63" s="50" t="inlineStr"/>
-      <c r="J63" s="35" t="inlineStr"/>
-      <c r="K63" s="42" t="inlineStr"/>
+      <c r="J63" s="41" t="inlineStr"/>
+      <c r="K63" s="41" t="inlineStr"/>
       <c r="L63" s="35" t="inlineStr"/>
       <c r="M63" s="37" t="inlineStr"/>
     </row>
@@ -3681,70 +3676,66 @@
       <c r="C64" s="49" t="n"/>
       <c r="D64" s="32" t="n"/>
       <c r="E64" s="49" t="n">
-        <v>316</v>
+        <v>245</v>
       </c>
       <c r="F64" s="32" t="inlineStr">
         <is>
-          <t>Arduino-Processing通信確認</t>
+          <t>ADSRパラメータ調整</t>
         </is>
       </c>
       <c r="G64" s="33" t="inlineStr">
         <is>
-          <t>長野・長山・慶田/中村・尾添</t>
+          <t>中村・尾添</t>
         </is>
       </c>
       <c r="H64" s="34" t="inlineStr"/>
       <c r="I64" s="50" t="inlineStr"/>
       <c r="J64" s="35" t="inlineStr"/>
-      <c r="K64" s="42" t="inlineStr"/>
+      <c r="K64" s="41" t="inlineStr"/>
       <c r="L64" s="35" t="inlineStr"/>
       <c r="M64" s="37" t="inlineStr"/>
     </row>
     <row r="65" ht="15" customHeight="1">
-      <c r="A65" s="23" t="inlineStr"/>
-      <c r="B65" s="24" t="inlineStr"/>
-      <c r="C65" s="25" t="n">
-        <v>320</v>
-      </c>
-      <c r="D65" s="26" t="inlineStr">
-        <is>
-          <t>単体テスト（U1-U4）</t>
-        </is>
-      </c>
-      <c r="E65" s="27" t="n"/>
-      <c r="F65" s="27" t="n"/>
-      <c r="G65" s="27" t="n"/>
-      <c r="H65" s="27" t="n"/>
-      <c r="I65" s="27" t="n"/>
-      <c r="J65" s="27" t="n"/>
-      <c r="K65" s="27" t="n"/>
-      <c r="L65" s="27" t="n"/>
-      <c r="M65" s="28" t="n"/>
+      <c r="A65" s="18" t="n">
+        <v>300</v>
+      </c>
+      <c r="B65" s="19" t="inlineStr">
+        <is>
+          <t>テストフェーズ</t>
+        </is>
+      </c>
+      <c r="C65" s="20" t="n"/>
+      <c r="D65" s="21" t="n"/>
+      <c r="E65" s="20" t="n"/>
+      <c r="F65" s="20" t="n"/>
+      <c r="G65" s="20" t="n"/>
+      <c r="H65" s="20" t="n"/>
+      <c r="I65" s="20" t="n"/>
+      <c r="J65" s="20" t="n"/>
+      <c r="K65" s="20" t="n"/>
+      <c r="L65" s="20" t="n"/>
+      <c r="M65" s="21" t="n"/>
     </row>
     <row r="66" ht="14" customHeight="1">
-      <c r="A66" s="47" t="n"/>
-      <c r="B66" s="48" t="n"/>
-      <c r="C66" s="49" t="n"/>
-      <c r="D66" s="32" t="n"/>
-      <c r="E66" s="49" t="n">
-        <v>321</v>
-      </c>
-      <c r="F66" s="32" t="inlineStr">
-        <is>
-          <t>センサーISR・テンポ推定単体テスト</t>
-        </is>
-      </c>
-      <c r="G66" s="33" t="inlineStr">
-        <is>
-          <t>長野・慶田</t>
-        </is>
-      </c>
-      <c r="H66" s="34" t="inlineStr"/>
-      <c r="I66" s="50" t="inlineStr"/>
-      <c r="J66" s="35" t="inlineStr"/>
-      <c r="K66" s="35" t="inlineStr"/>
-      <c r="L66" s="42" t="inlineStr"/>
-      <c r="M66" s="37" t="inlineStr"/>
+      <c r="A66" s="23" t="inlineStr"/>
+      <c r="B66" s="24" t="inlineStr"/>
+      <c r="C66" s="25" t="n">
+        <v>310</v>
+      </c>
+      <c r="D66" s="26" t="inlineStr">
+        <is>
+          <t>事前確認テスト（P1-P6）</t>
+        </is>
+      </c>
+      <c r="E66" s="27" t="n"/>
+      <c r="F66" s="27" t="n"/>
+      <c r="G66" s="27" t="n"/>
+      <c r="H66" s="27" t="n"/>
+      <c r="I66" s="27" t="n"/>
+      <c r="J66" s="27" t="n"/>
+      <c r="K66" s="27" t="n"/>
+      <c r="L66" s="27" t="n"/>
+      <c r="M66" s="28" t="n"/>
     </row>
     <row r="67" ht="14" customHeight="1">
       <c r="A67" s="47" t="n"/>
@@ -3752,11 +3743,11 @@
       <c r="C67" s="49" t="n"/>
       <c r="D67" s="32" t="n"/>
       <c r="E67" s="49" t="n">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="F67" s="32" t="inlineStr">
         <is>
-          <t>状態機械単体テスト</t>
+          <t>赤外線センサー精度確認</t>
         </is>
       </c>
       <c r="G67" s="33" t="inlineStr">
@@ -3767,8 +3758,8 @@
       <c r="H67" s="34" t="inlineStr"/>
       <c r="I67" s="50" t="inlineStr"/>
       <c r="J67" s="35" t="inlineStr"/>
-      <c r="K67" s="35" t="inlineStr"/>
-      <c r="L67" s="42" t="inlineStr"/>
+      <c r="K67" s="42" t="inlineStr"/>
+      <c r="L67" s="35" t="inlineStr"/>
       <c r="M67" s="37" t="inlineStr"/>
     </row>
     <row r="68" ht="14" customHeight="1">
@@ -3777,23 +3768,23 @@
       <c r="C68" s="49" t="n"/>
       <c r="D68" s="32" t="n"/>
       <c r="E68" s="49" t="n">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="F68" s="32" t="inlineStr">
         <is>
-          <t>楽譜進行・シリアル送信単体テスト</t>
+          <t>フォトTr検出距離確認</t>
         </is>
       </c>
       <c r="G68" s="33" t="inlineStr">
         <is>
-          <t>長山・慶田</t>
+          <t>長見・飛田/長野・慶田</t>
         </is>
       </c>
       <c r="H68" s="34" t="inlineStr"/>
       <c r="I68" s="50" t="inlineStr"/>
       <c r="J68" s="35" t="inlineStr"/>
-      <c r="K68" s="35" t="inlineStr"/>
-      <c r="L68" s="42" t="inlineStr"/>
+      <c r="K68" s="42" t="inlineStr"/>
+      <c r="L68" s="35" t="inlineStr"/>
       <c r="M68" s="37" t="inlineStr"/>
     </row>
     <row r="69" ht="14" customHeight="1">
@@ -3802,36 +3793,30 @@
       <c r="C69" s="49" t="n"/>
       <c r="D69" s="32" t="n"/>
       <c r="E69" s="49" t="n">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="F69" s="32" t="inlineStr">
         <is>
-          <t>音色合成・エフェクト単体テスト</t>
+          <t>LED輝度・フォトTr検出確認</t>
         </is>
       </c>
       <c r="G69" s="33" t="inlineStr">
         <is>
-          <t>中村・尾添</t>
+          <t>長見・飛田/長野・慶田</t>
         </is>
       </c>
       <c r="H69" s="34" t="inlineStr"/>
       <c r="I69" s="50" t="inlineStr"/>
       <c r="J69" s="35" t="inlineStr"/>
-      <c r="K69" s="35" t="inlineStr"/>
-      <c r="L69" s="42" t="inlineStr"/>
+      <c r="K69" s="42" t="inlineStr"/>
+      <c r="L69" s="35" t="inlineStr"/>
       <c r="M69" s="37" t="inlineStr"/>
     </row>
     <row r="70" ht="15" customHeight="1">
-      <c r="A70" s="23" t="inlineStr"/>
-      <c r="B70" s="24" t="inlineStr"/>
-      <c r="C70" s="25" t="n">
-        <v>330</v>
-      </c>
-      <c r="D70" s="26" t="inlineStr">
-        <is>
-          <t>結合テスト（C1-C3）</t>
-        </is>
-      </c>
+      <c r="A70" s="47" t="n"/>
+      <c r="B70" s="48" t="n"/>
+      <c r="C70" s="49" t="n"/>
+      <c r="D70" s="32" t="n"/>
       <c r="E70" s="27" t="n"/>
       <c r="F70" s="27" t="n"/>
       <c r="G70" s="27" t="n"/>
@@ -3848,23 +3833,23 @@
       <c r="C71" s="49" t="n"/>
       <c r="D71" s="32" t="n"/>
       <c r="E71" s="49" t="n">
-        <v>331</v>
+        <v>315</v>
       </c>
       <c r="F71" s="32" t="inlineStr">
         <is>
-          <t>Arduino-Processing遅延測定</t>
+          <t>サーボ最大BPM確認</t>
         </is>
       </c>
       <c r="G71" s="33" t="inlineStr">
         <is>
-          <t>長野・長山・慶田/中村・尾添</t>
+          <t>長見・飛田</t>
         </is>
       </c>
       <c r="H71" s="34" t="inlineStr"/>
       <c r="I71" s="50" t="inlineStr"/>
       <c r="J71" s="35" t="inlineStr"/>
-      <c r="K71" s="35" t="inlineStr"/>
-      <c r="L71" s="42" t="inlineStr"/>
+      <c r="K71" s="42" t="inlineStr"/>
+      <c r="L71" s="35" t="inlineStr"/>
       <c r="M71" s="37" t="inlineStr"/>
     </row>
     <row r="72" ht="14" customHeight="1">
@@ -3873,61 +3858,51 @@
       <c r="C72" s="49" t="n"/>
       <c r="D72" s="32" t="n"/>
       <c r="E72" s="49" t="n">
-        <v>332</v>
-      </c>
-      <c r="F72" s="32" t="inlineStr">
-        <is>
-          <t>同期・テンポ追従確認</t>
+        <v>316</v>
+      </c>
+      <c r="F72" s="65" t="inlineStr">
+        <is>
+          <t>Arduino-Processing通信確認</t>
         </is>
       </c>
       <c r="G72" s="33" t="inlineStr">
         <is>
-          <t>長野・長山・慶田</t>
+          <t>長野・長山・慶田/中村・尾添</t>
         </is>
       </c>
       <c r="H72" s="34" t="inlineStr"/>
       <c r="I72" s="50" t="inlineStr"/>
       <c r="J72" s="35" t="inlineStr"/>
-      <c r="K72" s="35" t="inlineStr"/>
-      <c r="L72" s="42" t="inlineStr"/>
-      <c r="M72" s="43" t="inlineStr"/>
+      <c r="K72" s="42" t="inlineStr"/>
+      <c r="L72" s="35" t="inlineStr"/>
+      <c r="M72" s="37" t="inlineStr"/>
     </row>
     <row r="73" ht="14" customHeight="1">
-      <c r="A73" s="47" t="n"/>
-      <c r="B73" s="48" t="n"/>
-      <c r="C73" s="49" t="n"/>
-      <c r="D73" s="32" t="n"/>
-      <c r="E73" s="49" t="n">
-        <v>333</v>
-      </c>
-      <c r="F73" s="32" t="inlineStr">
-        <is>
-          <t>フェルマータ動作確認</t>
-        </is>
-      </c>
-      <c r="G73" s="33" t="inlineStr">
-        <is>
-          <t>長野・長山・慶田/中村・尾添</t>
-        </is>
-      </c>
-      <c r="H73" s="34" t="inlineStr"/>
-      <c r="I73" s="50" t="inlineStr"/>
-      <c r="J73" s="35" t="inlineStr"/>
-      <c r="K73" s="35" t="inlineStr"/>
-      <c r="L73" s="42" t="inlineStr"/>
-      <c r="M73" s="43" t="inlineStr"/>
+      <c r="A73" s="23" t="inlineStr"/>
+      <c r="B73" s="24" t="inlineStr"/>
+      <c r="C73" s="25" t="n">
+        <v>320</v>
+      </c>
+      <c r="D73" s="26" t="inlineStr">
+        <is>
+          <t>単体テスト（U1-U4）</t>
+        </is>
+      </c>
+      <c r="E73" s="27" t="n"/>
+      <c r="F73" s="27" t="n"/>
+      <c r="G73" s="27" t="n"/>
+      <c r="H73" s="27" t="n"/>
+      <c r="I73" s="27" t="n"/>
+      <c r="J73" s="27" t="n"/>
+      <c r="K73" s="27" t="n"/>
+      <c r="L73" s="27" t="n"/>
+      <c r="M73" s="28" t="n"/>
     </row>
     <row r="74" ht="15" customHeight="1">
-      <c r="A74" s="23" t="inlineStr"/>
-      <c r="B74" s="24" t="inlineStr"/>
-      <c r="C74" s="25" t="n">
-        <v>340</v>
-      </c>
-      <c r="D74" s="26" t="inlineStr">
-        <is>
-          <t>システムテスト（S1-S3）</t>
-        </is>
-      </c>
+      <c r="A74" s="47" t="n"/>
+      <c r="B74" s="48" t="n"/>
+      <c r="C74" s="49" t="n"/>
+      <c r="D74" s="32" t="n"/>
       <c r="E74" s="27" t="n"/>
       <c r="F74" s="27" t="n"/>
       <c r="G74" s="27" t="n"/>
@@ -3944,24 +3919,24 @@
       <c r="C75" s="49" t="n"/>
       <c r="D75" s="32" t="n"/>
       <c r="E75" s="49" t="n">
-        <v>341</v>
+        <v>322</v>
       </c>
       <c r="F75" s="32" t="inlineStr">
         <is>
-          <t>通し演奏テスト</t>
+          <t>状態機械単体テスト</t>
         </is>
       </c>
       <c r="G75" s="33" t="inlineStr">
         <is>
-          <t>全員</t>
+          <t>長野・慶田</t>
         </is>
       </c>
       <c r="H75" s="34" t="inlineStr"/>
       <c r="I75" s="50" t="inlineStr"/>
       <c r="J75" s="35" t="inlineStr"/>
       <c r="K75" s="35" t="inlineStr"/>
-      <c r="L75" s="35" t="inlineStr"/>
-      <c r="M75" s="43" t="inlineStr"/>
+      <c r="L75" s="42" t="inlineStr"/>
+      <c r="M75" s="37" t="inlineStr"/>
     </row>
     <row r="76" ht="14" customHeight="1">
       <c r="A76" s="47" t="n"/>
@@ -3969,24 +3944,24 @@
       <c r="C76" s="49" t="n"/>
       <c r="D76" s="32" t="n"/>
       <c r="E76" s="49" t="n">
-        <v>342</v>
+        <v>323</v>
       </c>
       <c r="F76" s="32" t="inlineStr">
         <is>
-          <t>拍タイミング精度評価</t>
+          <t>楽譜進行・シリアル送信単体テスト</t>
         </is>
       </c>
       <c r="G76" s="33" t="inlineStr">
         <is>
-          <t>全員</t>
+          <t>長山・慶田</t>
         </is>
       </c>
       <c r="H76" s="34" t="inlineStr"/>
       <c r="I76" s="50" t="inlineStr"/>
       <c r="J76" s="35" t="inlineStr"/>
       <c r="K76" s="35" t="inlineStr"/>
-      <c r="L76" s="35" t="inlineStr"/>
-      <c r="M76" s="43" t="inlineStr"/>
+      <c r="L76" s="42" t="inlineStr"/>
+      <c r="M76" s="37" t="inlineStr"/>
     </row>
     <row r="77" ht="14" customHeight="1">
       <c r="A77" s="47" t="n"/>
@@ -3994,63 +3969,256 @@
       <c r="C77" s="49" t="n"/>
       <c r="D77" s="32" t="n"/>
       <c r="E77" s="49" t="n">
-        <v>343</v>
+        <v>324</v>
       </c>
       <c r="F77" s="32" t="inlineStr">
         <is>
-          <t>テンポ変化・フェルマータ完全確認</t>
+          <t>音色合成・エフェクト単体テスト</t>
         </is>
       </c>
       <c r="G77" s="33" t="inlineStr">
         <is>
-          <t>全員</t>
+          <t>中村・尾添</t>
         </is>
       </c>
       <c r="H77" s="34" t="inlineStr"/>
       <c r="I77" s="50" t="inlineStr"/>
       <c r="J77" s="35" t="inlineStr"/>
       <c r="K77" s="35" t="inlineStr"/>
-      <c r="L77" s="35" t="inlineStr"/>
-      <c r="M77" s="43" t="inlineStr"/>
+      <c r="L77" s="42" t="inlineStr"/>
+      <c r="M77" s="37" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="23" t="inlineStr"/>
+      <c r="B78" s="24" t="inlineStr"/>
+      <c r="C78" s="25" t="n">
+        <v>330</v>
+      </c>
+      <c r="D78" s="26" t="inlineStr">
+        <is>
+          <t>結合テスト（C1-C3）</t>
+        </is>
+      </c>
+      <c r="E78" s="27" t="n"/>
+      <c r="F78" s="27" t="n"/>
+      <c r="G78" s="27" t="n"/>
+      <c r="H78" s="27" t="n"/>
+      <c r="I78" s="27" t="n"/>
+      <c r="J78" s="27" t="n"/>
+      <c r="K78" s="27" t="n"/>
+      <c r="L78" s="27" t="n"/>
+      <c r="M78" s="28" t="n"/>
     </row>
     <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="44" t="inlineStr">
+      <c r="A79" s="47" t="n"/>
+      <c r="B79" s="48" t="n"/>
+      <c r="C79" s="49" t="n"/>
+      <c r="D79" s="32" t="n"/>
+      <c r="E79" s="49" t="n">
+        <v>331</v>
+      </c>
+      <c r="F79" s="65" t="inlineStr">
+        <is>
+          <t>Arduino-Processing遅延測定</t>
+        </is>
+      </c>
+      <c r="G79" s="33" t="inlineStr">
+        <is>
+          <t>長野・長山・慶田/中村・尾添</t>
+        </is>
+      </c>
+      <c r="H79" s="34" t="inlineStr"/>
+      <c r="I79" s="50" t="inlineStr"/>
+      <c r="J79" s="35" t="inlineStr"/>
+      <c r="K79" s="35" t="inlineStr"/>
+      <c r="L79" s="42" t="inlineStr"/>
+      <c r="M79" s="37" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="47" t="n"/>
+      <c r="B80" s="48" t="n"/>
+      <c r="C80" s="49" t="n"/>
+      <c r="D80" s="32" t="n"/>
+      <c r="E80" s="49" t="n">
+        <v>332</v>
+      </c>
+      <c r="F80" s="32" t="inlineStr">
+        <is>
+          <t>同期・テンポ追従確認</t>
+        </is>
+      </c>
+      <c r="G80" s="33" t="inlineStr">
+        <is>
+          <t>長野・長山・慶田</t>
+        </is>
+      </c>
+      <c r="H80" s="34" t="inlineStr"/>
+      <c r="I80" s="50" t="inlineStr"/>
+      <c r="J80" s="35" t="inlineStr"/>
+      <c r="K80" s="35" t="inlineStr"/>
+      <c r="L80" s="42" t="inlineStr"/>
+      <c r="M80" s="43" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="47" t="n"/>
+      <c r="B81" s="48" t="n"/>
+      <c r="C81" s="49" t="n"/>
+      <c r="D81" s="32" t="n"/>
+      <c r="E81" s="49" t="n">
+        <v>333</v>
+      </c>
+      <c r="F81" s="32" t="inlineStr">
+        <is>
+          <t>フェルマータ動作確認</t>
+        </is>
+      </c>
+      <c r="G81" s="33" t="inlineStr">
+        <is>
+          <t>長野・長山・慶田/中村・尾添</t>
+        </is>
+      </c>
+      <c r="H81" s="34" t="inlineStr"/>
+      <c r="I81" s="50" t="inlineStr"/>
+      <c r="J81" s="35" t="inlineStr"/>
+      <c r="K81" s="35" t="inlineStr"/>
+      <c r="L81" s="42" t="inlineStr"/>
+      <c r="M81" s="43" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="23" t="inlineStr"/>
+      <c r="B82" s="24" t="inlineStr"/>
+      <c r="C82" s="25" t="n">
+        <v>340</v>
+      </c>
+      <c r="D82" s="26" t="inlineStr">
+        <is>
+          <t>システムテスト（S1-S3）</t>
+        </is>
+      </c>
+      <c r="E82" s="27" t="n"/>
+      <c r="F82" s="27" t="n"/>
+      <c r="G82" s="27" t="n"/>
+      <c r="H82" s="27" t="n"/>
+      <c r="I82" s="27" t="n"/>
+      <c r="J82" s="27" t="n"/>
+      <c r="K82" s="27" t="n"/>
+      <c r="L82" s="27" t="n"/>
+      <c r="M82" s="28" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="47" t="n"/>
+      <c r="B83" s="48" t="n"/>
+      <c r="C83" s="49" t="n"/>
+      <c r="D83" s="32" t="n"/>
+      <c r="E83" s="49" t="n">
+        <v>341</v>
+      </c>
+      <c r="F83" s="32" t="inlineStr">
+        <is>
+          <t>通し演奏テスト</t>
+        </is>
+      </c>
+      <c r="G83" s="33" t="inlineStr">
+        <is>
+          <t>全員</t>
+        </is>
+      </c>
+      <c r="H83" s="34" t="inlineStr"/>
+      <c r="I83" s="50" t="inlineStr"/>
+      <c r="J83" s="35" t="inlineStr"/>
+      <c r="K83" s="35" t="inlineStr"/>
+      <c r="L83" s="35" t="inlineStr"/>
+      <c r="M83" s="43" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="47" t="n"/>
+      <c r="B84" s="48" t="n"/>
+      <c r="C84" s="49" t="n"/>
+      <c r="D84" s="32" t="n"/>
+      <c r="E84" s="49" t="n">
+        <v>342</v>
+      </c>
+      <c r="F84" s="32" t="inlineStr">
+        <is>
+          <t>拍タイミング精度評価</t>
+        </is>
+      </c>
+      <c r="G84" s="33" t="inlineStr">
+        <is>
+          <t>全員</t>
+        </is>
+      </c>
+      <c r="H84" s="34" t="inlineStr"/>
+      <c r="I84" s="50" t="inlineStr"/>
+      <c r="J84" s="35" t="inlineStr"/>
+      <c r="K84" s="35" t="inlineStr"/>
+      <c r="L84" s="35" t="inlineStr"/>
+      <c r="M84" s="43" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="47" t="n"/>
+      <c r="B85" s="48" t="n"/>
+      <c r="C85" s="49" t="n"/>
+      <c r="D85" s="32" t="n"/>
+      <c r="E85" s="49" t="n">
+        <v>343</v>
+      </c>
+      <c r="F85" s="32" t="inlineStr">
+        <is>
+          <t>テンポ変化・フェルマータ完全確認</t>
+        </is>
+      </c>
+      <c r="G85" s="33" t="inlineStr">
+        <is>
+          <t>全員</t>
+        </is>
+      </c>
+      <c r="H85" s="34" t="inlineStr"/>
+      <c r="I85" s="50" t="inlineStr"/>
+      <c r="J85" s="35" t="inlineStr"/>
+      <c r="K85" s="35" t="inlineStr"/>
+      <c r="L85" s="35" t="inlineStr"/>
+      <c r="M85" s="43" t="inlineStr"/>
+    </row>
+    <row r="86"/>
+    <row r="87">
+      <c r="A87" s="44" t="inlineStr">
         <is>
           <t>凡例</t>
         </is>
       </c>
-      <c r="B79" s="55" t="inlineStr"/>
-      <c r="C79" s="45" t="inlineStr">
+      <c r="B87" s="55" t="inlineStr"/>
+      <c r="C87" s="45" t="inlineStr">
         <is>
           <t>担当A（長見・飛田）</t>
         </is>
       </c>
-      <c r="D79" s="56" t="inlineStr"/>
-      <c r="E79" s="45" t="inlineStr">
+      <c r="D87" s="56" t="inlineStr"/>
+      <c r="E87" s="45" t="inlineStr">
         <is>
           <t>担当B（長野・慶田）</t>
         </is>
       </c>
-      <c r="F79" s="57" t="inlineStr"/>
-      <c r="G79" s="45" t="inlineStr">
+      <c r="F87" s="57" t="inlineStr"/>
+      <c r="G87" s="45" t="inlineStr">
         <is>
           <t>担当C（長山・慶田）</t>
         </is>
       </c>
-      <c r="H79" s="58" t="inlineStr"/>
-      <c r="I79" s="45" t="inlineStr">
+      <c r="H87" s="58" t="inlineStr"/>
+      <c r="I87" s="45" t="inlineStr">
         <is>
           <t>担当D（中村・尾添）</t>
         </is>
       </c>
-      <c r="J79" s="59" t="inlineStr"/>
-      <c r="K79" s="45" t="inlineStr">
+      <c r="J87" s="59" t="inlineStr"/>
+      <c r="K87" s="45" t="inlineStr">
         <is>
           <t>テストフェーズ</t>
         </is>
       </c>
-      <c r="L79" s="60" t="inlineStr"/>
-      <c r="M79" s="45" t="inlineStr">
+      <c r="L87" s="60" t="inlineStr"/>
+      <c r="M87" s="45" t="inlineStr">
         <is>
           <t>バッファー週</t>
         </is>
